--- a/artfynd/A 57430-2025 artfynd.xlsx
+++ b/artfynd/A 57430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>79518117</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320421.4461411391</v>
+        <v>320421</v>
       </c>
       <c r="R2" t="n">
-        <v>6585178.62960666</v>
+        <v>6585179</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2019-06-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,10 +780,254 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Ek, Gabriella Johansson</t>
+          <t>Johanna Ek, Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91880515</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Slarverud, väg S175, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>320428</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6585167</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Fågelvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Moa Naalisvaara Engman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Ek, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118162953</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slarverud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>320437</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6585172</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Fågelvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sex blommande plantor i ytterslänt, östra sidan av vägen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Tengström, Christian Teittinen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
